--- a/invoice_automation/clients/northsky_comm/templates/SupplierLists.xlsx
+++ b/invoice_automation/clients/northsky_comm/templates/SupplierLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHONCODE\PDFInvoiceExtract\invoice_automation\clients\northsky_comm\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC6054E-7636-43AE-A0E0-E90234482B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BECDD0A-79EA-4191-BB34-5D8F5C560B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35895" yWindow="1335" windowWidth="14400" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VENDORS" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14185" uniqueCount="6041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14186" uniqueCount="6042">
   <si>
     <t>Name of Supplier</t>
   </si>
@@ -18160,6 +18160,9 @@
   </si>
   <si>
     <t>DONOTREPLYTOTHISEMAIL@fleetpride.com</t>
+  </si>
+  <si>
+    <t>R01711</t>
   </si>
 </sst>
 </file>
@@ -64483,6 +64486,9 @@
       <c r="C12" s="2" t="s">
         <v>6007</v>
       </c>
+      <c r="F12" t="s">
+        <v>6041</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">

--- a/invoice_automation/clients/northsky_comm/templates/SupplierLists.xlsx
+++ b/invoice_automation/clients/northsky_comm/templates/SupplierLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHONCODE\PDFInvoiceExtract\invoice_automation\clients\northsky_comm\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BECDD0A-79EA-4191-BB34-5D8F5C560B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E73133C-1DB5-4C64-BA42-6BA8077A09A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35895" yWindow="1335" windowWidth="14400" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VENDORS" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14186" uniqueCount="6042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14187" uniqueCount="6043">
   <si>
     <t>Name of Supplier</t>
   </si>
@@ -18163,6 +18163,9 @@
   </si>
   <si>
     <t>R01711</t>
+  </si>
+  <si>
+    <t>R02666</t>
   </si>
 </sst>
 </file>
@@ -64431,6 +64434,9 @@
       <c r="C7" t="s">
         <v>6006</v>
       </c>
+      <c r="F7" t="s">
+        <v>6042</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">

--- a/invoice_automation/clients/northsky_comm/templates/SupplierLists.xlsx
+++ b/invoice_automation/clients/northsky_comm/templates/SupplierLists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\PDFInvoiceExtract\invoice_automation\clients\northsky_comm\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515AB130-0E5E-44E5-838A-1740F6EC6521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B85741-5F11-45E9-94CF-0DC277C6FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VENDORS" sheetId="1" r:id="rId1"/>

--- a/invoice_automation/clients/northsky_comm/templates/SupplierLists.xlsx
+++ b/invoice_automation/clients/northsky_comm/templates/SupplierLists.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHONCODE\PDFInvoiceExtract\invoice_automation\clients\northsky_comm\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B42814-3B72-45BF-9D83-87A362F152AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3FB58D-1EFD-4EAB-B9DC-CD07895D277D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="13725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VENDORS" sheetId="1" r:id="rId1"/>
     <sheet name="Parsers" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">VENDORS!$A$1:$L$1409</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">VENDORS!$A$1:$L$1447</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11858" uniqueCount="4995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12008" uniqueCount="5088">
   <si>
     <t>Name of Supplier</t>
   </si>
@@ -14910,9 +14910,6 @@
     <t>475270100</t>
   </si>
   <si>
-    <t>CONCUR TECHNOLOGIES, INC.</t>
-  </si>
-  <si>
     <t>VCONCU</t>
   </si>
   <si>
@@ -15022,6 +15019,288 @@
   </si>
   <si>
     <t>R01712</t>
+  </si>
+  <si>
+    <t>NAPA AUTO PARTS SELMA</t>
+  </si>
+  <si>
+    <t>MOLALLA NAPA</t>
+  </si>
+  <si>
+    <t>NAPA AUTO PARTS EPHRATA</t>
+  </si>
+  <si>
+    <t>R00976</t>
+  </si>
+  <si>
+    <t>CESSCO</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>MRP</t>
+  </si>
+  <si>
+    <t>R02780</t>
+  </si>
+  <si>
+    <t>R02674</t>
+  </si>
+  <si>
+    <t>R01743</t>
+  </si>
+  <si>
+    <t>R01649</t>
+  </si>
+  <si>
+    <t>R01158</t>
+  </si>
+  <si>
+    <t>NAPA COOS BAY</t>
+  </si>
+  <si>
+    <t>R01376</t>
+  </si>
+  <si>
+    <t>BUD CLARY</t>
+  </si>
+  <si>
+    <t>V08747</t>
+  </si>
+  <si>
+    <t>V08748</t>
+  </si>
+  <si>
+    <t>V08755</t>
+  </si>
+  <si>
+    <t>V08756</t>
+  </si>
+  <si>
+    <t>V08757</t>
+  </si>
+  <si>
+    <t>V08827</t>
+  </si>
+  <si>
+    <t>V08828</t>
+  </si>
+  <si>
+    <t>V08829</t>
+  </si>
+  <si>
+    <t>V08830</t>
+  </si>
+  <si>
+    <t>V08832</t>
+  </si>
+  <si>
+    <t>V08833</t>
+  </si>
+  <si>
+    <t>V08834</t>
+  </si>
+  <si>
+    <t>V08835</t>
+  </si>
+  <si>
+    <t>V08836</t>
+  </si>
+  <si>
+    <t>V08838</t>
+  </si>
+  <si>
+    <t>V08840</t>
+  </si>
+  <si>
+    <t>V08841</t>
+  </si>
+  <si>
+    <t>V08843</t>
+  </si>
+  <si>
+    <t>V08847</t>
+  </si>
+  <si>
+    <t>V08849</t>
+  </si>
+  <si>
+    <t>V08850</t>
+  </si>
+  <si>
+    <t>V08853</t>
+  </si>
+  <si>
+    <t>V08854</t>
+  </si>
+  <si>
+    <t>V08856</t>
+  </si>
+  <si>
+    <t>V08861</t>
+  </si>
+  <si>
+    <t>V08863</t>
+  </si>
+  <si>
+    <t>V08865</t>
+  </si>
+  <si>
+    <t>V08867</t>
+  </si>
+  <si>
+    <t>V08869</t>
+  </si>
+  <si>
+    <t>V08875</t>
+  </si>
+  <si>
+    <t>V08877</t>
+  </si>
+  <si>
+    <t>V08878</t>
+  </si>
+  <si>
+    <t>V08879</t>
+  </si>
+  <si>
+    <t>V08885</t>
+  </si>
+  <si>
+    <t>V08886</t>
+  </si>
+  <si>
+    <t>V08896</t>
+  </si>
+  <si>
+    <t>V08908</t>
+  </si>
+  <si>
+    <t>V08909</t>
+  </si>
+  <si>
+    <t>V08910</t>
+  </si>
+  <si>
+    <t>UMBRELLA PLUMBING</t>
+  </si>
+  <si>
+    <t>BALES MOBILE MIX CONCRETE</t>
+  </si>
+  <si>
+    <t>VERSALIFT NATIONAL PARTS DIST CTR</t>
+  </si>
+  <si>
+    <t>FRANKLIN RIDGE SAND &amp; GRAVEL</t>
+  </si>
+  <si>
+    <t>ABBOTTS PRO-POWER</t>
+  </si>
+  <si>
+    <t>PLEASANTON READY MIX CONCRETE INC.</t>
+  </si>
+  <si>
+    <t>CENTENNIAL AGGREGATE INC</t>
+  </si>
+  <si>
+    <t>SW MAINTENANCE CORP</t>
+  </si>
+  <si>
+    <t>RAIN ROCK CASINO HOTEL RESORT</t>
+  </si>
+  <si>
+    <t>PLUMETTAZ AMERICA CORP</t>
+  </si>
+  <si>
+    <t>UNITED SITE SERVICES INC</t>
+  </si>
+  <si>
+    <t>CHASE SUITE HOTEL</t>
+  </si>
+  <si>
+    <t>PACIFIC TREE MANAGEMENT</t>
+  </si>
+  <si>
+    <t>BRIAN ELDRIDGE</t>
+  </si>
+  <si>
+    <t>LINCOLN CROSSING COMMUNITY</t>
+  </si>
+  <si>
+    <t>YREKA TRANSFER LLC</t>
+  </si>
+  <si>
+    <t>ELION MATTHEW GUERRERO</t>
+  </si>
+  <si>
+    <t>PHOENIX WINSUPPLY INC</t>
+  </si>
+  <si>
+    <t>WILSON PARTS CORP</t>
+  </si>
+  <si>
+    <t>ARROWHEAD ELECTRIC LLC</t>
+  </si>
+  <si>
+    <t>C.E. ANDERSON LLC</t>
+  </si>
+  <si>
+    <t>ROBERT HALF INC</t>
+  </si>
+  <si>
+    <t>COEUR D'ALENE TRACTOR CO</t>
+  </si>
+  <si>
+    <t>CODY COLEMAN</t>
+  </si>
+  <si>
+    <t>CITY OF MONUMENT</t>
+  </si>
+  <si>
+    <t>NWC OFFICE FURNITURE</t>
+  </si>
+  <si>
+    <t>UMPQUA SAND &amp; GRAVEL</t>
+  </si>
+  <si>
+    <t>SIX RIVERS PORTABLE TOILETS LLC</t>
+  </si>
+  <si>
+    <t>DAN DAVIDSON</t>
+  </si>
+  <si>
+    <t>HELENA SAND &amp; GRAVEL</t>
+  </si>
+  <si>
+    <t>ASBURY ENVIRONMENTAL SERVICES</t>
+  </si>
+  <si>
+    <t>HYDRAULIC SUPPLY COMPANY</t>
+  </si>
+  <si>
+    <t>BEST WESTERN RENO AIRPORT</t>
+  </si>
+  <si>
+    <t>CORNERSTONE FENCING INC.</t>
+  </si>
+  <si>
+    <t>MOUNTAIN WEST HOLDING CO</t>
+  </si>
+  <si>
+    <t>CALIFORNIA ROCK CRUSHERS</t>
+  </si>
+  <si>
+    <t>KH PAINTING</t>
+  </si>
+  <si>
+    <t>ENTERPRISE ELECTRIC AND RENTAL</t>
+  </si>
+  <si>
+    <t>COAST COUNTIES PETERBILT</t>
+  </si>
+  <si>
+    <t>ONCUR TECHNOLOGIES, INC.</t>
   </si>
 </sst>
 </file>
@@ -15057,10 +15336,36 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -15069,7 +15374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -15077,6 +15382,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -15420,7 +15731,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L1409"/>
+  <dimension ref="A1:L1448"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.75" bestFit="1" customWidth="1"/>
@@ -23049,7 +23360,7 @@
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
-        <v>4977</v>
+        <v>4976</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>1382</v>
@@ -38857,7 +39168,7 @@
     </row>
     <row r="858" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A858" s="2" t="s">
-        <v>4984</v>
+        <v>4983</v>
       </c>
       <c r="B858" s="2" t="s">
         <v>3161</v>
@@ -53554,7 +53865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1408" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1408" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1408" s="2" t="s">
         <v>4953</v>
       </c>
@@ -53583,33 +53894,462 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1409" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1409" s="2" t="s">
+    <row r="1409" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1409" s="4" t="s">
+        <v>5048</v>
+      </c>
+      <c r="B1409" s="2" t="s">
+        <v>5009</v>
+      </c>
+      <c r="C1409" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1410" s="4" t="s">
+        <v>5049</v>
+      </c>
+      <c r="B1410" s="4" t="s">
+        <v>5010</v>
+      </c>
+      <c r="C1410" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1411" s="4" t="s">
+        <v>5050</v>
+      </c>
+      <c r="B1411" s="4" t="s">
+        <v>5011</v>
+      </c>
+      <c r="C1411" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1412" s="4" t="s">
+        <v>5051</v>
+      </c>
+      <c r="B1412" s="4" t="s">
+        <v>5012</v>
+      </c>
+      <c r="C1412" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1413" s="4" t="s">
+        <v>5052</v>
+      </c>
+      <c r="B1413" s="4" t="s">
+        <v>5013</v>
+      </c>
+      <c r="C1413" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1414" s="4" t="s">
+        <v>5053</v>
+      </c>
+      <c r="B1414" s="4" t="s">
+        <v>5014</v>
+      </c>
+      <c r="C1414" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1415" s="4" t="s">
+        <v>5054</v>
+      </c>
+      <c r="B1415" s="4" t="s">
+        <v>5015</v>
+      </c>
+      <c r="C1415" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1416" s="4" t="s">
+        <v>5055</v>
+      </c>
+      <c r="B1416" s="4" t="s">
+        <v>5016</v>
+      </c>
+      <c r="C1416" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1417" s="4" t="s">
+        <v>5056</v>
+      </c>
+      <c r="B1417" s="4" t="s">
+        <v>5017</v>
+      </c>
+      <c r="C1417" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1418" s="4" t="s">
+        <v>5057</v>
+      </c>
+      <c r="B1418" s="4" t="s">
+        <v>5018</v>
+      </c>
+      <c r="C1418" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1419" s="4" t="s">
+        <v>5058</v>
+      </c>
+      <c r="B1419" s="4" t="s">
+        <v>5019</v>
+      </c>
+      <c r="C1419" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1420" s="4" t="s">
+        <v>5059</v>
+      </c>
+      <c r="B1420" s="4" t="s">
+        <v>5020</v>
+      </c>
+      <c r="C1420" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1421" s="4" t="s">
+        <v>5060</v>
+      </c>
+      <c r="B1421" s="4" t="s">
+        <v>5021</v>
+      </c>
+      <c r="C1421" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1422" s="4" t="s">
+        <v>5061</v>
+      </c>
+      <c r="B1422" s="4" t="s">
+        <v>5022</v>
+      </c>
+      <c r="C1422" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1423" s="4" t="s">
+        <v>5062</v>
+      </c>
+      <c r="B1423" s="4" t="s">
+        <v>5023</v>
+      </c>
+      <c r="C1423" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1424" s="4" t="s">
+        <v>5063</v>
+      </c>
+      <c r="B1424" s="4" t="s">
+        <v>5024</v>
+      </c>
+      <c r="C1424" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1425" s="4" t="s">
+        <v>5064</v>
+      </c>
+      <c r="B1425" s="4" t="s">
+        <v>5025</v>
+      </c>
+      <c r="C1425" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1426" s="4" t="s">
+        <v>5065</v>
+      </c>
+      <c r="B1426" s="4" t="s">
+        <v>5026</v>
+      </c>
+      <c r="C1426" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1427" s="4" t="s">
+        <v>5066</v>
+      </c>
+      <c r="B1427" s="4" t="s">
+        <v>5027</v>
+      </c>
+      <c r="C1427" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1428" s="4" t="s">
+        <v>5067</v>
+      </c>
+      <c r="B1428" s="4" t="s">
+        <v>5028</v>
+      </c>
+      <c r="C1428" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1429" s="4" t="s">
+        <v>5068</v>
+      </c>
+      <c r="B1429" s="4" t="s">
+        <v>5029</v>
+      </c>
+      <c r="C1429" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1430" s="4" t="s">
+        <v>5069</v>
+      </c>
+      <c r="B1430" s="4" t="s">
+        <v>5030</v>
+      </c>
+      <c r="C1430" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1431" s="4" t="s">
+        <v>5070</v>
+      </c>
+      <c r="B1431" s="4" t="s">
+        <v>5031</v>
+      </c>
+      <c r="C1431" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1432" s="4" t="s">
+        <v>5071</v>
+      </c>
+      <c r="B1432" s="4" t="s">
+        <v>5032</v>
+      </c>
+      <c r="C1432" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1433" s="4" t="s">
+        <v>5072</v>
+      </c>
+      <c r="B1433" s="4" t="s">
+        <v>5033</v>
+      </c>
+      <c r="C1433" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1434" s="4" t="s">
+        <v>5073</v>
+      </c>
+      <c r="B1434" s="4" t="s">
+        <v>5034</v>
+      </c>
+      <c r="C1434" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1435" s="4" t="s">
+        <v>5074</v>
+      </c>
+      <c r="B1435" s="4" t="s">
+        <v>5035</v>
+      </c>
+      <c r="C1435" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1436" s="4" t="s">
+        <v>5075</v>
+      </c>
+      <c r="B1436" s="4" t="s">
+        <v>5036</v>
+      </c>
+      <c r="C1436" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1437" s="4" t="s">
+        <v>5076</v>
+      </c>
+      <c r="B1437" s="4" t="s">
+        <v>5037</v>
+      </c>
+      <c r="C1437" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1438" s="4" t="s">
+        <v>5077</v>
+      </c>
+      <c r="B1438" s="4" t="s">
+        <v>5038</v>
+      </c>
+      <c r="C1438" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1439" s="4" t="s">
+        <v>5078</v>
+      </c>
+      <c r="B1439" s="4" t="s">
+        <v>5039</v>
+      </c>
+      <c r="C1439" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1440" s="4" t="s">
+        <v>5079</v>
+      </c>
+      <c r="B1440" s="4" t="s">
+        <v>5040</v>
+      </c>
+      <c r="C1440" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1441" s="4" t="s">
+        <v>5080</v>
+      </c>
+      <c r="B1441" s="4" t="s">
+        <v>5041</v>
+      </c>
+      <c r="C1441" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1442" s="4" t="s">
+        <v>5081</v>
+      </c>
+      <c r="B1442" s="4" t="s">
+        <v>5042</v>
+      </c>
+      <c r="C1442" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1443" s="4" t="s">
+        <v>5082</v>
+      </c>
+      <c r="B1443" s="4" t="s">
+        <v>5043</v>
+      </c>
+      <c r="C1443" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1444" s="4" t="s">
+        <v>5083</v>
+      </c>
+      <c r="B1444" s="4" t="s">
+        <v>5044</v>
+      </c>
+      <c r="C1444" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1445" s="4" t="s">
+        <v>5084</v>
+      </c>
+      <c r="B1445" s="4" t="s">
+        <v>5045</v>
+      </c>
+      <c r="C1445" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1446" s="4" t="s">
+        <v>5085</v>
+      </c>
+      <c r="B1446" s="4" t="s">
+        <v>5046</v>
+      </c>
+      <c r="C1446" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1447" s="4" t="s">
+        <v>5086</v>
+      </c>
+      <c r="B1447" s="4" t="s">
+        <v>5047</v>
+      </c>
+      <c r="C1447" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1447" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E1447" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1447" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1447" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1448" s="5" t="s">
+        <v>5087</v>
+      </c>
+      <c r="B1448" s="2" t="s">
         <v>4957</v>
       </c>
-      <c r="B1409" s="2" t="s">
-        <v>4958</v>
-      </c>
-      <c r="C1409" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1409" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="E1409" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1409" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K1409" s="2" t="s">
-        <v>14</v>
+      <c r="C1448" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1409" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L1409">
-      <sortCondition ref="B1:B1409"/>
+  <autoFilter ref="A1:L1408" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L1408">
+      <sortCondition ref="B1:B1408"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -53618,7 +54358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB95720F-FF21-424B-9325-52AFC9D9096D}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -53629,33 +54369,33 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>4976</v>
+        <v>4975</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>4962</v>
+        <v>4961</v>
       </c>
       <c r="D1" t="s">
+        <v>4973</v>
+      </c>
+      <c r="E1" t="s">
         <v>4974</v>
       </c>
-      <c r="E1" t="s">
-        <v>4975</v>
-      </c>
       <c r="F1" t="s">
-        <v>4973</v>
+        <v>4972</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>4959</v>
+        <v>4958</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>545</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -53672,13 +54412,13 @@
         <v>1100</v>
       </c>
       <c r="C3" t="s">
-        <v>4960</v>
+        <v>4959</v>
       </c>
       <c r="D3">
         <v>51000230</v>
       </c>
       <c r="E3" t="s">
-        <v>4970</v>
+        <v>4969</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -53686,27 +54426,27 @@
         <v>2393</v>
       </c>
       <c r="C4" t="s">
-        <v>4960</v>
+        <v>4959</v>
       </c>
       <c r="D4">
         <v>51000230</v>
       </c>
       <c r="E4" t="s">
-        <v>4970</v>
+        <v>4969</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4963</v>
+        <v>4962</v>
       </c>
       <c r="C5" t="s">
-        <v>4960</v>
+        <v>4959</v>
       </c>
       <c r="D5">
         <v>51000230</v>
       </c>
       <c r="E5" t="s">
-        <v>4970</v>
+        <v>4969</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -53714,13 +54454,13 @@
         <v>886</v>
       </c>
       <c r="C6" t="s">
-        <v>4960</v>
+        <v>4959</v>
       </c>
       <c r="D6">
         <v>51000230</v>
       </c>
       <c r="E6" t="s">
-        <v>4983</v>
+        <v>4982</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -53731,24 +54471,24 @@
         <v>2647</v>
       </c>
       <c r="C7" t="s">
-        <v>4960</v>
+        <v>4959</v>
       </c>
       <c r="F7" t="s">
-        <v>4986</v>
+        <v>4985</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>4964</v>
+        <v>4963</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
       <c r="D8">
         <v>51000320</v>
       </c>
       <c r="E8" t="s">
-        <v>4971</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -53756,29 +54496,29 @@
         <v>130</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>4965</v>
+        <v>4964</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
       <c r="D10">
         <v>51000100</v>
       </c>
       <c r="E10" t="s">
-        <v>4972</v>
+        <v>4971</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>4966</v>
+        <v>4965</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -53789,101 +54529,104 @@
         <v>2248</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
       <c r="F12" t="s">
-        <v>4985</v>
+        <v>4984</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>4967</v>
+        <v>4966</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>4968</v>
+        <v>4967</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>4969</v>
+        <v>4968</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>1419</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>4977</v>
+        <v>4976</v>
       </c>
       <c r="B16" t="s">
         <v>1382</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
       <c r="D16">
         <v>51000230</v>
       </c>
       <c r="E16" t="s">
-        <v>4980</v>
+        <v>4979</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>4979</v>
+        <v>4978</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
       <c r="D17">
         <v>51000100</v>
       </c>
       <c r="E17" t="s">
-        <v>4972</v>
+        <v>4971</v>
+      </c>
+      <c r="F17" t="s">
+        <v>4997</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>4978</v>
+        <v>4977</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>4981</v>
+        <v>4980</v>
       </c>
       <c r="C19" t="s">
-        <v>4960</v>
+        <v>4959</v>
       </c>
       <c r="D19">
         <v>51000230</v>
       </c>
       <c r="E19" t="s">
-        <v>4982</v>
+        <v>4981</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>4987</v>
+        <v>4986</v>
       </c>
       <c r="B20" t="s">
         <v>1071</v>
       </c>
       <c r="F20" t="s">
-        <v>4988</v>
+        <v>4987</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -53896,18 +54639,18 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>4990</v>
+        <v>4989</v>
       </c>
       <c r="B22" t="s">
         <v>1765</v>
       </c>
       <c r="F22" t="s">
-        <v>4989</v>
+        <v>4988</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>4991</v>
+        <v>4990</v>
       </c>
       <c r="B23" t="s">
         <v>2759</v>
@@ -53915,7 +54658,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>4992</v>
+        <v>4991</v>
       </c>
       <c r="B24" t="s">
         <v>2278</v>
@@ -53923,13 +54666,138 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>4993</v>
+        <v>4992</v>
       </c>
       <c r="B25" t="s">
         <v>2244</v>
       </c>
       <c r="F25" t="s">
+        <v>4993</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>4994</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>4995</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>4996</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B29" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>5006</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F30" t="s">
+        <v>5007</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>4998</v>
+      </c>
+      <c r="D31">
+        <v>51000230</v>
+      </c>
+      <c r="E31" t="s">
+        <v>4999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>5000</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F33" t="s">
+        <v>5001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>283</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2668</v>
+      </c>
+      <c r="F34" t="s">
+        <v>5002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>243</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2387</v>
+      </c>
+      <c r="F35" t="s">
+        <v>5003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>212</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F36" t="s">
+        <v>5004</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>582</v>
+      </c>
+      <c r="B37" t="s">
+        <v>583</v>
+      </c>
+      <c r="F37" t="s">
+        <v>5005</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>5008</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1896</v>
       </c>
     </row>
   </sheetData>
